--- a/examples/word/tables.xlsx
+++ b/examples/word/tables.xlsx
@@ -3,8 +3,8 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="Performance" sheetId="2" r:id="R6aa9335363df425a"/>
-    <x:sheet name="Summary" sheetId="3" r:id="R5c64374edb68427b"/>
+    <x:sheet name="Performance" sheetId="2" r:id="R172664a0108d4b05"/>
+    <x:sheet name="Summary" sheetId="3" r:id="R9e70a0dfd7744648"/>
   </x:sheets>
   <x:calcPr fullCalcOnLoad="1"/>
 </x:workbook>
